--- a/artfynd/A 41068-2024 artfynd.xlsx
+++ b/artfynd/A 41068-2024 artfynd.xlsx
@@ -2064,11 +2064,11 @@
         <v>120647985</v>
       </c>
       <c r="B15" t="n">
-        <v>57364</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/artfynd/A 41068-2024 artfynd.xlsx
+++ b/artfynd/A 41068-2024 artfynd.xlsx
@@ -2064,7 +2064,7 @@
         <v>120647985</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 41068-2024 artfynd.xlsx
+++ b/artfynd/A 41068-2024 artfynd.xlsx
@@ -2064,7 +2064,7 @@
         <v>120647985</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 41068-2024 artfynd.xlsx
+++ b/artfynd/A 41068-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120647959</v>
+        <v>120647937</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413288</v>
+        <v>414128</v>
       </c>
       <c r="R2" t="n">
-        <v>6929674</v>
+        <v>6929601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120647937</v>
+        <v>120647985</v>
       </c>
       <c r="B3" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>414128</v>
+        <v>414297</v>
       </c>
       <c r="R3" t="n">
-        <v>6929601</v>
+        <v>6929739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120647955</v>
+        <v>120647938</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413368</v>
+        <v>413547</v>
       </c>
       <c r="R4" t="n">
-        <v>6929690</v>
+        <v>6929731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack ganska sentida</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120647950</v>
+        <v>120647939</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413614</v>
+        <v>413804</v>
       </c>
       <c r="R5" t="n">
-        <v>6929630</v>
+        <v>6929790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120647956</v>
+        <v>120647940</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413364</v>
+        <v>413833</v>
       </c>
       <c r="R6" t="n">
-        <v>6929695</v>
+        <v>6929827</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120647948</v>
+        <v>120647942</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413554</v>
+        <v>413838</v>
       </c>
       <c r="R7" t="n">
-        <v>6929531</v>
+        <v>6929807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120647984</v>
+        <v>120647944</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413364</v>
+        <v>414051</v>
       </c>
       <c r="R8" t="n">
-        <v>6929526</v>
+        <v>6929767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120647940</v>
+        <v>120647945</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413833</v>
+        <v>413838</v>
       </c>
       <c r="R9" t="n">
-        <v>6929827</v>
+        <v>6929732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120647944</v>
+        <v>120647946</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>414051</v>
+        <v>413747</v>
       </c>
       <c r="R10" t="n">
-        <v>6929767</v>
+        <v>6929637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120647953</v>
+        <v>120647947</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413650</v>
+        <v>413727</v>
       </c>
       <c r="R11" t="n">
-        <v>6929656</v>
+        <v>6929569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120647954</v>
+        <v>120647948</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413613</v>
+        <v>413554</v>
       </c>
       <c r="R12" t="n">
-        <v>6929688</v>
+        <v>6929531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,15 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120647945</v>
+        <v>120647949</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413838</v>
+        <v>413584</v>
       </c>
       <c r="R13" t="n">
-        <v>6929732</v>
+        <v>6929593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,15 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120647965</v>
+        <v>120647950</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413146</v>
+        <v>413614</v>
       </c>
       <c r="R14" t="n">
-        <v>6929455</v>
+        <v>6929630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,15 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120647985</v>
+        <v>120647951</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,16 +2007,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2101,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>414297</v>
+        <v>413614</v>
       </c>
       <c r="R15" t="n">
-        <v>6929739</v>
+        <v>6929615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2071,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,15 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120647942</v>
+        <v>120647953</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413838</v>
+        <v>413650</v>
       </c>
       <c r="R16" t="n">
-        <v>6929807</v>
+        <v>6929656</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2173,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,15 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120647958</v>
+        <v>120647954</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413280</v>
+        <v>413613</v>
       </c>
       <c r="R17" t="n">
-        <v>6929692</v>
+        <v>6929688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2275,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,15 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120647961</v>
+        <v>120647955</v>
       </c>
       <c r="B18" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>413323</v>
+        <v>413368</v>
       </c>
       <c r="R18" t="n">
-        <v>6929495</v>
+        <v>6929690</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2377,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska sentida</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,15 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120647962</v>
+        <v>120647956</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>413201</v>
+        <v>413364</v>
       </c>
       <c r="R19" t="n">
-        <v>6929531</v>
+        <v>6929695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,15 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120647988</v>
+        <v>120647957</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>413345</v>
+        <v>413118</v>
       </c>
       <c r="R20" t="n">
-        <v>6929485</v>
+        <v>6929650</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,15 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120647947</v>
+        <v>120647958</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>413727</v>
+        <v>413280</v>
       </c>
       <c r="R21" t="n">
-        <v>6929569</v>
+        <v>6929692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,15 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120647957</v>
+        <v>120647959</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>413118</v>
+        <v>413288</v>
       </c>
       <c r="R22" t="n">
-        <v>6929650</v>
+        <v>6929674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2785,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,15 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120647939</v>
+        <v>120647960</v>
       </c>
       <c r="B23" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,10 +2847,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>413804</v>
+        <v>413269</v>
       </c>
       <c r="R23" t="n">
-        <v>6929790</v>
+        <v>6929572</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,15 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120647960</v>
+        <v>120647961</v>
       </c>
       <c r="B24" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>413269</v>
+        <v>413323</v>
       </c>
       <c r="R24" t="n">
-        <v>6929572</v>
+        <v>6929495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,15 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120647986</v>
+        <v>120647962</v>
       </c>
       <c r="B25" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,21 +3027,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>413516</v>
+        <v>413201</v>
       </c>
       <c r="R25" t="n">
-        <v>6929717</v>
+        <v>6929531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3087,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,15 +3118,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120647987</v>
+        <v>120647964</v>
       </c>
       <c r="B26" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,21 +3129,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>413212</v>
+        <v>413190</v>
       </c>
       <c r="R26" t="n">
-        <v>6929508</v>
+        <v>6929429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,6 +3189,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,15 +3220,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120647946</v>
+        <v>120647965</v>
       </c>
       <c r="B27" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>413747</v>
+        <v>413146</v>
       </c>
       <c r="R27" t="n">
-        <v>6929637</v>
+        <v>6929455</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,15 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120647938</v>
+        <v>120647966</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>413547</v>
+        <v>413136</v>
       </c>
       <c r="R28" t="n">
-        <v>6929731</v>
+        <v>6929425</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,15 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120647983</v>
+        <v>120647971</v>
       </c>
       <c r="B29" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3584,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>413356</v>
+        <v>413179</v>
       </c>
       <c r="R29" t="n">
-        <v>6929537</v>
+        <v>6929415</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,15 +3526,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120647951</v>
+        <v>120647981</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,10 +3561,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>413614</v>
+        <v>413365</v>
       </c>
       <c r="R30" t="n">
-        <v>6929615</v>
+        <v>6929470</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3601,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,15 +3628,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120647949</v>
+        <v>120647982</v>
       </c>
       <c r="B31" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>413584</v>
+        <v>413350</v>
       </c>
       <c r="R31" t="n">
-        <v>6929593</v>
+        <v>6929480</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,6 +3727,210 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120647983</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gravaråsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>413356</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6929537</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120647984</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gravaråsarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>413364</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6929526</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
